--- a/Valuaciones_USA/FISV_valuaciones_hits_por_anio.xlsx
+++ b/Valuaciones_USA/FISV_valuaciones_hits_por_anio.xlsx
@@ -1,75 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>Año</t>
-  </si>
-  <si>
-    <t>Metodo</t>
-  </si>
-  <si>
-    <t>Valor</t>
-  </si>
-  <si>
-    <t>hit</t>
-  </si>
-  <si>
-    <t>tth_weeks</t>
-  </si>
-  <si>
-    <t>hit_date</t>
-  </si>
-  <si>
-    <t>side</t>
-  </si>
-  <si>
-    <t>Mes</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -77,36 +45,86 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -394,37 +412,2159 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G76"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Metodo</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>hit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>tth_weeks</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>hit_date</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Dec2011</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GF_Value_Guru</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>40910</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>at_target</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dec2012</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GF_Value_Guru</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Dec2013</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GF_Value_Guru</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Dec2014</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GF_Value_Guru</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Dec2015</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GF_Value_Guru</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>36.22</v>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Dec2016</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GF_Value_Guru</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>42765</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Dec2017</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GF_Value_Guru</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>58.86</v>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Dec2018</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GF_Value_Guru</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>68.84999999999999</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>43479</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Dec2019</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GF_Value_Guru</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>99.79000000000001</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>43885</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Dec2020</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GF_Value_Guru</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>119.97</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>44200</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>at_target</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Dec2021</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GF_Value_Guru</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>125.77</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>68</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>45040</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Dec2022</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GF_Value_Guru</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>127.59</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>45040</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Dec2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GF_Value_Guru</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>128.7</v>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>at_target</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Dec2024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GF_Value_Guru</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>142.65</v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>28</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>45859</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sep2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GF_Value_Guru</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>166.5</v>
+      </c>
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Dec2011</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_EPS</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>86.39489378186235</v>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Dec2012</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_EPS</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>41.97027952831783</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>114</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>42079</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Dec2013</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_EPS</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>49.8224618798622</v>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>93</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>42296</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Dec2014</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_EPS</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>55.0368490453224</v>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>70</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>42499</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Dec2015</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_EPS</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>61.49907604795203</v>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>60</v>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>42793</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Dec2016</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_EPS</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>68.29840910773416</v>
+      </c>
+      <c r="D22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>39</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>43010</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Dec2017</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_EPS</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>76.55420372597899</v>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>43150</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Dec2018</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_EPS</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>102.1088077992134</v>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>27</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>43661</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Dec2019</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_EPS</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>132.5887303088351</v>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>61</v>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>44263</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Dec2020</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_EPS</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>170.001577854043</v>
+      </c>
+      <c r="D26" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Dec2021</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_EPS</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>141.291100100083</v>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>101</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>45271</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Dec2022</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_EPS</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>193.175822034423</v>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>91</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>45565</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Dec2023</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_EPS</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>180.1138111369964</v>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>34</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>45530</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Dec2024</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_EPS</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>225.6649726275598</v>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>45684</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sep2025</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_EPS</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>237.0170745957838</v>
+      </c>
+      <c r="D31" t="b">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Dec2011</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_FCF</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>63.49968948865133</v>
+      </c>
+      <c r="D32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Dec2012</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_FCF</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>19.47122092702704</v>
+      </c>
+      <c r="D33" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>41281</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>at_target</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Dec2013</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_FCF</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>31.23570417690573</v>
+      </c>
+      <c r="D34" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16</v>
+      </c>
+      <c r="F34" s="1" t="n">
+        <v>41757</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Dec2014</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_FCF</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>48.30360059582965</v>
+      </c>
+      <c r="D35" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>39</v>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>42282</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Dec2015</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_FCF</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>43.69759552761533</v>
+      </c>
+      <c r="D36" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="1" t="n">
+        <v>42373</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>at_target</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Dec2016</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_FCF</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>54.43750518320675</v>
+      </c>
+      <c r="D37" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="1" t="n">
+        <v>42737</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>at_target</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Dec2017</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_FCF</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>62.25125400648635</v>
+      </c>
+      <c r="D38" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="1" t="n">
+        <v>43101</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>at_target</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Dec2018</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_FCF</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>83.84482937970108</v>
+      </c>
+      <c r="D39" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F39" s="1" t="n">
+        <v>43486</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Dec2019</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_FCF</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>88.15062938450721</v>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>10</v>
+      </c>
+      <c r="F40" s="1" t="n">
+        <v>43906</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Dec2020</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_FCF</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>153.1133501683379</v>
+      </c>
+      <c r="D41" t="b">
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Dec2021</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_FCF</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>132.2377572121808</v>
+      </c>
+      <c r="D42" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>77</v>
+      </c>
+      <c r="F42" s="1" t="n">
+        <v>45103</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Dec2022</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_FCF</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>142.2553582267516</v>
+      </c>
+      <c r="D43" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>49</v>
+      </c>
+      <c r="F43" s="1" t="n">
+        <v>45271</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Dec2023</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_FCF</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>139.2292611250791</v>
+      </c>
+      <c r="D44" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>at_target</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Dec2024</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_FCF</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>214.2879137943163</v>
+      </c>
+      <c r="D45" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="1" t="n">
+        <v>45663</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>at_target</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sep2025</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Intrinsic_CAGR_FCF</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>212.9444938182342</v>
+      </c>
+      <c r="D46" t="b">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Dec2011</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Mediana</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>54.18956396390117</v>
+      </c>
+      <c r="D47" t="b">
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Dec2012</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Mediana</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>34.99092365406051</v>
+      </c>
+      <c r="D48" t="b">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>94</v>
+      </c>
+      <c r="F48" s="1" t="n">
+        <v>41939</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Dec2013</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Mediana</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>43.28210219934192</v>
+      </c>
+      <c r="D49" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>75</v>
+      </c>
+      <c r="F49" s="1" t="n">
+        <v>42170</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Dec2014</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Mediana</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>47.61979866752259</v>
+      </c>
+      <c r="D50" t="b">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>32</v>
+      </c>
+      <c r="F50" s="1" t="n">
+        <v>42233</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Dec2015</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Mediana</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>54.98387462916148</v>
+      </c>
+      <c r="D51" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>18</v>
+      </c>
+      <c r="F51" s="1" t="n">
+        <v>42499</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Dec2016</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Mediana</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>63.39908768809752</v>
+      </c>
+      <c r="D52" t="b">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>16</v>
+      </c>
+      <c r="F52" s="1" t="n">
+        <v>42849</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Dec2017</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Mediana</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>72.6581914920304</v>
+      </c>
+      <c r="D53" t="b">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="1" t="n">
+        <v>43108</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Dec2018</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Mediana</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>81.96980082158832</v>
+      </c>
+      <c r="D54" t="b">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="1" t="n">
+        <v>43479</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Dec2019</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Mediana</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>108.5692530924473</v>
+      </c>
+      <c r="D55" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>7</v>
+      </c>
+      <c r="F55" s="1" t="n">
+        <v>43885</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Dec2020</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Mediana</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>141.50302671456</v>
+      </c>
+      <c r="D56" t="b">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>153</v>
+      </c>
+      <c r="F56" s="1" t="n">
+        <v>45271</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Dec2021</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Mediana</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>183.9253260736817</v>
+      </c>
+      <c r="D57" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>138</v>
+      </c>
+      <c r="F57" s="1" t="n">
+        <v>45530</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Dec2022</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Mediana</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>172.4909825605091</v>
+      </c>
+      <c r="D58" t="b">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>82</v>
+      </c>
+      <c r="F58" s="1" t="n">
+        <v>45502</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Dec2023</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Mediana</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>160.2050315604632</v>
+      </c>
+      <c r="D59" t="b">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>11</v>
+      </c>
+      <c r="F59" s="1" t="n">
+        <v>45369</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Dec2024</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Mediana</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>198.791371204633</v>
+      </c>
+      <c r="D60" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="1" t="n">
+        <v>45663</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>at_target</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Sep2025</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Mediana</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>218.5557323762378</v>
+      </c>
+      <c r="D61" t="b">
+        <v>0</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Dec2011</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Weighted</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>86.39489378186235</v>
+      </c>
+      <c r="D62" t="b">
+        <v>0</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Dec2012</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Weighted</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>38.64963263228512</v>
+      </c>
+      <c r="D63" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>105</v>
+      </c>
+      <c r="F63" s="1" t="n">
+        <v>42016</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Dec2013</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Weighted</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>46.8309076250611</v>
+      </c>
+      <c r="D64" t="b">
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>82</v>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>42219</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Dec2014</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Weighted</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>51.58572605882303</v>
+      </c>
+      <c r="D65" t="b">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>59</v>
+      </c>
+      <c r="F65" s="1" t="n">
+        <v>42422</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Dec2015</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Weighted</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>58.5288308842211</v>
+      </c>
+      <c r="D66" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>27</v>
+      </c>
+      <c r="F66" s="1" t="n">
+        <v>42562</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Dec2016</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Weighted</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>65.14270144348448</v>
+      </c>
+      <c r="D67" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>20</v>
+      </c>
+      <c r="F67" s="1" t="n">
+        <v>42877</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Dec2017</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Weighted</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>72.58480073344052</v>
+      </c>
+      <c r="D68" t="b">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="1" t="n">
+        <v>43108</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Dec2018</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Weighted</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>90.13685700195659</v>
+      </c>
+      <c r="D69" t="b">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
+      <c r="F69" s="1" t="n">
+        <v>43493</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Dec2019</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Weighted</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>133.7545568693638</v>
+      </c>
+      <c r="D70" t="b">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>68</v>
+      </c>
+      <c r="F70" s="1" t="n">
+        <v>44312</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Dec2020</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Weighted</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>159.8624766590561</v>
+      </c>
+      <c r="D71" t="b">
+        <v>0</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Dec2021</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Weighted</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>181.9257556677028</v>
+      </c>
+      <c r="D72" t="b">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>138</v>
+      </c>
+      <c r="F72" s="1" t="n">
+        <v>45530</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Dec2022</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Weighted</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>204.2600664367377</v>
+      </c>
+      <c r="D73" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>93</v>
+      </c>
+      <c r="F73" s="1" t="n">
+        <v>45579</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Dec2023</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Weighted</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>186.1058213641676</v>
+      </c>
+      <c r="D74" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>37</v>
+      </c>
+      <c r="F74" s="1" t="n">
+        <v>45551</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Dec2024</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Weighted</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>225.8205806209201</v>
+      </c>
+      <c r="D75" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3</v>
+      </c>
+      <c r="F75" s="1" t="n">
+        <v>45684</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Sep2025</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Intrinsic_EPS_Weighted</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>210.0686010261905</v>
+      </c>
+      <c r="D76" t="b">
+        <v>0</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>